--- a/artfynd/A 37833-2025 artfynd.xlsx
+++ b/artfynd/A 37833-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127448660</v>
+        <v>127450593</v>
       </c>
       <c r="B2" t="n">
-        <v>80118</v>
+        <v>80121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Marstrandmyran, Marstrandmyran, Hls</t>
+          <t>Hivikilen, Hivikilen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499461</v>
+        <v>499290</v>
       </c>
       <c r="R2" t="n">
-        <v>6845884</v>
+        <v>6846237</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127450593</v>
+        <v>127448660</v>
       </c>
       <c r="B3" t="n">
-        <v>80117</v>
+        <v>80122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hivikilen, Hivikilen, Hls</t>
+          <t>Marstrandmyran, Marstrandmyran, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499290</v>
+        <v>499461</v>
       </c>
       <c r="R3" t="n">
-        <v>6846237</v>
+        <v>6845884</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,12 +857,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -872,7 +872,7 @@
         <v>127448470</v>
       </c>
       <c r="B4" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127448841</v>
       </c>
       <c r="B5" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127448201</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>127449070</v>
       </c>
       <c r="B7" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>127450133</v>
       </c>
       <c r="B8" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>127450046</v>
       </c>
       <c r="B9" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>127449822</v>
       </c>
       <c r="B10" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>127448817</v>
       </c>
       <c r="B11" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>127449478</v>
       </c>
       <c r="B12" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>127448386</v>
       </c>
       <c r="B13" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37833-2025 artfynd.xlsx
+++ b/artfynd/A 37833-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127450593</v>
+        <v>127448660</v>
       </c>
       <c r="B2" t="n">
-        <v>80121</v>
+        <v>80122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hivikilen, Hivikilen, Hls</t>
+          <t>Marstrandmyran, Marstrandmyran, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499290</v>
+        <v>499461</v>
       </c>
       <c r="R2" t="n">
-        <v>6846237</v>
+        <v>6845884</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127448660</v>
+        <v>127450593</v>
       </c>
       <c r="B3" t="n">
-        <v>80122</v>
+        <v>80121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Marstrandmyran, Marstrandmyran, Hls</t>
+          <t>Hivikilen, Hivikilen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499461</v>
+        <v>499290</v>
       </c>
       <c r="R3" t="n">
-        <v>6845884</v>
+        <v>6846237</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,12 +857,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 37833-2025 artfynd.xlsx
+++ b/artfynd/A 37833-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127448660</v>
+        <v>127450593</v>
       </c>
       <c r="B2" t="n">
-        <v>80122</v>
+        <v>80121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Marstrandmyran, Marstrandmyran, Hls</t>
+          <t>Hivikilen, Hivikilen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499461</v>
+        <v>499290</v>
       </c>
       <c r="R2" t="n">
-        <v>6845884</v>
+        <v>6846237</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127450593</v>
+        <v>127448660</v>
       </c>
       <c r="B3" t="n">
-        <v>80121</v>
+        <v>80122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hivikilen, Hivikilen, Hls</t>
+          <t>Marstrandmyran, Marstrandmyran, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499290</v>
+        <v>499461</v>
       </c>
       <c r="R3" t="n">
-        <v>6846237</v>
+        <v>6845884</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,12 +857,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
         <v>127448201</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127449478</v>
+        <v>127448386</v>
       </c>
       <c r="B12" t="n">
-        <v>57821</v>
+        <v>80121</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1675,37 +1675,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Marstrandmyran, Marstrandmyran, Hls</t>
+          <t>Hivikilen, Hivikilen, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499572</v>
+        <v>499513</v>
       </c>
       <c r="R12" t="n">
-        <v>6845945</v>
+        <v>6845882</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1735,6 +1735,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Lunglav 4 meter från bandning i anmälan.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1749,22 +1754,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127448386</v>
+        <v>127449478</v>
       </c>
       <c r="B13" t="n">
-        <v>80121</v>
+        <v>57821</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1772,37 +1777,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hivikilen, Hivikilen, Hls</t>
+          <t>Marstrandmyran, Marstrandmyran, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499513</v>
+        <v>499572</v>
       </c>
       <c r="R13" t="n">
-        <v>6845882</v>
+        <v>6845945</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1832,11 +1837,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Lunglav 4 meter från bandning i anmälan.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1851,12 +1851,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 37833-2025 artfynd.xlsx
+++ b/artfynd/A 37833-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127450593</v>
+        <v>127448660</v>
       </c>
       <c r="B2" t="n">
-        <v>80121</v>
+        <v>80124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hivikilen, Hivikilen, Hls</t>
+          <t>Marstrandmyran, Marstrandmyran, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499290</v>
+        <v>499461</v>
       </c>
       <c r="R2" t="n">
-        <v>6846237</v>
+        <v>6845884</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127448660</v>
+        <v>127450593</v>
       </c>
       <c r="B3" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Marstrandmyran, Marstrandmyran, Hls</t>
+          <t>Hivikilen, Hivikilen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499461</v>
+        <v>499290</v>
       </c>
       <c r="R3" t="n">
-        <v>6845884</v>
+        <v>6846237</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,12 +857,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -872,7 +872,7 @@
         <v>127448470</v>
       </c>
       <c r="B4" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127448841</v>
       </c>
       <c r="B5" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127448201</v>
       </c>
       <c r="B6" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>127449070</v>
       </c>
       <c r="B7" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>127450133</v>
       </c>
       <c r="B8" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>127450046</v>
       </c>
       <c r="B9" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>127449822</v>
       </c>
       <c r="B10" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>127448817</v>
       </c>
       <c r="B11" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127448386</v>
+        <v>127449478</v>
       </c>
       <c r="B12" t="n">
-        <v>80121</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1675,37 +1675,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hivikilen, Hivikilen, Hls</t>
+          <t>Marstrandmyran, Marstrandmyran, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499513</v>
+        <v>499572</v>
       </c>
       <c r="R12" t="n">
-        <v>6845882</v>
+        <v>6845945</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1735,11 +1735,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Lunglav 4 meter från bandning i anmälan.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1754,22 +1749,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127449478</v>
+        <v>127448386</v>
       </c>
       <c r="B13" t="n">
-        <v>57821</v>
+        <v>80123</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1777,37 +1772,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Marstrandmyran, Marstrandmyran, Hls</t>
+          <t>Hivikilen, Hivikilen, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499572</v>
+        <v>499513</v>
       </c>
       <c r="R13" t="n">
-        <v>6845945</v>
+        <v>6845882</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1837,6 +1832,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Lunglav 4 meter från bandning i anmälan.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1851,12 +1851,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 37833-2025 artfynd.xlsx
+++ b/artfynd/A 37833-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127448660</v>
+        <v>127450593</v>
       </c>
       <c r="B2" t="n">
-        <v>80124</v>
+        <v>80123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Marstrandmyran, Marstrandmyran, Hls</t>
+          <t>Hivikilen, Hivikilen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499461</v>
+        <v>499290</v>
       </c>
       <c r="R2" t="n">
-        <v>6845884</v>
+        <v>6846237</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127450593</v>
+        <v>127448660</v>
       </c>
       <c r="B3" t="n">
-        <v>80123</v>
+        <v>80124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hivikilen, Hivikilen, Hls</t>
+          <t>Marstrandmyran, Marstrandmyran, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499290</v>
+        <v>499461</v>
       </c>
       <c r="R3" t="n">
-        <v>6846237</v>
+        <v>6845884</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,12 +857,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 37833-2025 artfynd.xlsx
+++ b/artfynd/A 37833-2025 artfynd.xlsx
@@ -1664,10 +1664,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127449478</v>
+        <v>127448386</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>80123</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1675,37 +1675,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Marstrandmyran, Marstrandmyran, Hls</t>
+          <t>Hivikilen, Hivikilen, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499572</v>
+        <v>499513</v>
       </c>
       <c r="R12" t="n">
-        <v>6845945</v>
+        <v>6845882</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1735,6 +1735,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Lunglav 4 meter från bandning i anmälan.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1749,22 +1754,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127448386</v>
+        <v>127449478</v>
       </c>
       <c r="B13" t="n">
-        <v>80123</v>
+        <v>57823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1772,37 +1777,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hivikilen, Hivikilen, Hls</t>
+          <t>Marstrandmyran, Marstrandmyran, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499513</v>
+        <v>499572</v>
       </c>
       <c r="R13" t="n">
-        <v>6845882</v>
+        <v>6845945</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1832,11 +1837,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Lunglav 4 meter från bandning i anmälan.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1851,12 +1851,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 37833-2025 artfynd.xlsx
+++ b/artfynd/A 37833-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127450593</v>
+        <v>127448660</v>
       </c>
       <c r="B2" t="n">
-        <v>80123</v>
+        <v>80124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hivikilen, Hivikilen, Hls</t>
+          <t>Marstrandmyran, Marstrandmyran, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499290</v>
+        <v>499461</v>
       </c>
       <c r="R2" t="n">
-        <v>6846237</v>
+        <v>6845884</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127448660</v>
+        <v>127450593</v>
       </c>
       <c r="B3" t="n">
-        <v>80124</v>
+        <v>80123</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Marstrandmyran, Marstrandmyran, Hls</t>
+          <t>Hivikilen, Hivikilen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499461</v>
+        <v>499290</v>
       </c>
       <c r="R3" t="n">
-        <v>6845884</v>
+        <v>6846237</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,12 +857,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 37833-2025 artfynd.xlsx
+++ b/artfynd/A 37833-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127448660</v>
+        <v>127450593</v>
       </c>
       <c r="B2" t="n">
-        <v>80124</v>
+        <v>80123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Marstrandmyran, Marstrandmyran, Hls</t>
+          <t>Hivikilen, Hivikilen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499461</v>
+        <v>499290</v>
       </c>
       <c r="R2" t="n">
-        <v>6845884</v>
+        <v>6846237</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127450593</v>
+        <v>127448660</v>
       </c>
       <c r="B3" t="n">
-        <v>80123</v>
+        <v>80124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hivikilen, Hivikilen, Hls</t>
+          <t>Marstrandmyran, Marstrandmyran, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499290</v>
+        <v>499461</v>
       </c>
       <c r="R3" t="n">
-        <v>6846237</v>
+        <v>6845884</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,12 +857,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
         <v>127448201</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127450133</v>
+        <v>127450046</v>
       </c>
       <c r="B8" t="n">
         <v>80123</v>
@@ -1306,10 +1306,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499514</v>
+        <v>499530</v>
       </c>
       <c r="R8" t="n">
-        <v>6846240</v>
+        <v>6846219</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1342,11 +1342,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>6 meter från bandning.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1373,7 +1368,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127450046</v>
+        <v>127450133</v>
       </c>
       <c r="B9" t="n">
         <v>80123</v>
@@ -1408,10 +1403,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499530</v>
+        <v>499514</v>
       </c>
       <c r="R9" t="n">
-        <v>6846219</v>
+        <v>6846240</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1444,6 +1439,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>6 meter från bandning.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1664,10 +1664,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127448386</v>
+        <v>127449478</v>
       </c>
       <c r="B12" t="n">
-        <v>80123</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1675,37 +1675,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hivikilen, Hivikilen, Hls</t>
+          <t>Marstrandmyran, Marstrandmyran, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499513</v>
+        <v>499572</v>
       </c>
       <c r="R12" t="n">
-        <v>6845882</v>
+        <v>6845945</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1735,11 +1735,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Lunglav 4 meter från bandning i anmälan.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1754,22 +1749,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127449478</v>
+        <v>127448386</v>
       </c>
       <c r="B13" t="n">
-        <v>57823</v>
+        <v>80123</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1777,37 +1772,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Marstrandmyran, Marstrandmyran, Hls</t>
+          <t>Hivikilen, Hivikilen, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499572</v>
+        <v>499513</v>
       </c>
       <c r="R13" t="n">
-        <v>6845945</v>
+        <v>6845882</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1837,6 +1832,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Lunglav 4 meter från bandning i anmälan.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1851,12 +1851,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 37833-2025 artfynd.xlsx
+++ b/artfynd/A 37833-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127450593</v>
       </c>
       <c r="B2" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127448660</v>
       </c>
       <c r="B3" t="n">
-        <v>80124</v>
+        <v>80127</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127448470</v>
       </c>
       <c r="B4" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127448841</v>
       </c>
       <c r="B5" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127448201</v>
       </c>
       <c r="B6" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>127449070</v>
       </c>
       <c r="B7" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,10 +1271,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127450046</v>
+        <v>127450133</v>
       </c>
       <c r="B8" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1306,10 +1306,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499530</v>
+        <v>499514</v>
       </c>
       <c r="R8" t="n">
-        <v>6846219</v>
+        <v>6846240</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1342,6 +1342,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>6 meter från bandning.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1368,10 +1373,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127450133</v>
+        <v>127450046</v>
       </c>
       <c r="B9" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1403,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>499514</v>
+        <v>499530</v>
       </c>
       <c r="R9" t="n">
-        <v>6846240</v>
+        <v>6846219</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1439,11 +1444,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>6 meter från bandning.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1473,7 +1473,7 @@
         <v>127449822</v>
       </c>
       <c r="B10" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>127448817</v>
       </c>
       <c r="B11" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127449478</v>
+        <v>127448386</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>80126</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1675,37 +1675,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Marstrandmyran, Marstrandmyran, Hls</t>
+          <t>Hivikilen, Hivikilen, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499572</v>
+        <v>499513</v>
       </c>
       <c r="R12" t="n">
-        <v>6845945</v>
+        <v>6845882</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1735,6 +1735,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Lunglav 4 meter från bandning i anmälan.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1749,22 +1754,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127448386</v>
+        <v>127449478</v>
       </c>
       <c r="B13" t="n">
-        <v>80123</v>
+        <v>57826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1772,37 +1777,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hivikilen, Hivikilen, Hls</t>
+          <t>Marstrandmyran, Marstrandmyran, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499513</v>
+        <v>499572</v>
       </c>
       <c r="R13" t="n">
-        <v>6845882</v>
+        <v>6845945</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1832,11 +1837,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Lunglav 4 meter från bandning i anmälan.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1851,12 +1851,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 37833-2025 artfynd.xlsx
+++ b/artfynd/A 37833-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127450593</v>
       </c>
       <c r="B2" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127448660</v>
       </c>
       <c r="B3" t="n">
-        <v>80127</v>
+        <v>80133</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127448470</v>
       </c>
       <c r="B4" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127448841</v>
       </c>
       <c r="B5" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127448201</v>
       </c>
       <c r="B6" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>127449070</v>
       </c>
       <c r="B7" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>127450133</v>
       </c>
       <c r="B8" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>127450046</v>
       </c>
       <c r="B9" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>127449822</v>
       </c>
       <c r="B10" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>127448817</v>
       </c>
       <c r="B11" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>127448386</v>
       </c>
       <c r="B12" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>127449478</v>
       </c>
       <c r="B13" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 37833-2025 artfynd.xlsx
+++ b/artfynd/A 37833-2025 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>127448201</v>
       </c>
       <c r="B6" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127448386</v>
+        <v>127449478</v>
       </c>
       <c r="B12" t="n">
-        <v>80132</v>
+        <v>57832</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1675,37 +1675,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hivikilen, Hivikilen, Hls</t>
+          <t>Marstrandmyran, Marstrandmyran, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499513</v>
+        <v>499572</v>
       </c>
       <c r="R12" t="n">
-        <v>6845882</v>
+        <v>6845945</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1735,11 +1735,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Lunglav 4 meter från bandning i anmälan.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1754,22 +1749,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127449478</v>
+        <v>127448386</v>
       </c>
       <c r="B13" t="n">
-        <v>57832</v>
+        <v>80132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1777,37 +1772,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Marstrandmyran, Marstrandmyran, Hls</t>
+          <t>Hivikilen, Hivikilen, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499572</v>
+        <v>499513</v>
       </c>
       <c r="R13" t="n">
-        <v>6845945</v>
+        <v>6845882</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1837,6 +1832,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Lunglav 4 meter från bandning i anmälan.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1851,12 +1851,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 37833-2025 artfynd.xlsx
+++ b/artfynd/A 37833-2025 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>127448201</v>
       </c>
       <c r="B6" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37833-2025 artfynd.xlsx
+++ b/artfynd/A 37833-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127450593</v>
+        <v>127448660</v>
       </c>
       <c r="B2" t="n">
-        <v>80132</v>
+        <v>80133</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hivikilen, Hivikilen, Hls</t>
+          <t>Marstrandmyran, Marstrandmyran, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499290</v>
+        <v>499461</v>
       </c>
       <c r="R2" t="n">
-        <v>6846237</v>
+        <v>6845884</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127448660</v>
+        <v>127450593</v>
       </c>
       <c r="B3" t="n">
-        <v>80133</v>
+        <v>80132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Marstrandmyran, Marstrandmyran, Hls</t>
+          <t>Hivikilen, Hivikilen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499461</v>
+        <v>499290</v>
       </c>
       <c r="R3" t="n">
-        <v>6845884</v>
+        <v>6846237</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,12 +857,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
         <v>127448201</v>
       </c>
       <c r="B6" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127449478</v>
+        <v>127448386</v>
       </c>
       <c r="B12" t="n">
-        <v>57832</v>
+        <v>80132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1675,37 +1675,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Marstrandmyran, Marstrandmyran, Hls</t>
+          <t>Hivikilen, Hivikilen, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499572</v>
+        <v>499513</v>
       </c>
       <c r="R12" t="n">
-        <v>6845945</v>
+        <v>6845882</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1735,6 +1735,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Lunglav 4 meter från bandning i anmälan.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1749,22 +1754,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127448386</v>
+        <v>127449478</v>
       </c>
       <c r="B13" t="n">
-        <v>80132</v>
+        <v>57832</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1772,37 +1777,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hivikilen, Hivikilen, Hls</t>
+          <t>Marstrandmyran, Marstrandmyran, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>499513</v>
+        <v>499572</v>
       </c>
       <c r="R13" t="n">
-        <v>6845882</v>
+        <v>6845945</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1832,11 +1837,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Lunglav 4 meter från bandning i anmälan.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1851,12 +1851,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 37833-2025 artfynd.xlsx
+++ b/artfynd/A 37833-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127448660</v>
+        <v>127450593</v>
       </c>
       <c r="B2" t="n">
-        <v>80133</v>
+        <v>80132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Marstrandmyran, Marstrandmyran, Hls</t>
+          <t>Hivikilen, Hivikilen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499461</v>
+        <v>499290</v>
       </c>
       <c r="R2" t="n">
-        <v>6845884</v>
+        <v>6846237</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127450593</v>
+        <v>127448660</v>
       </c>
       <c r="B3" t="n">
-        <v>80132</v>
+        <v>80133</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hivikilen, Hivikilen, Hls</t>
+          <t>Marstrandmyran, Marstrandmyran, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499290</v>
+        <v>499461</v>
       </c>
       <c r="R3" t="n">
-        <v>6846237</v>
+        <v>6845884</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,12 +857,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 37833-2025 artfynd.xlsx
+++ b/artfynd/A 37833-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127450593</v>
+        <v>127448660</v>
       </c>
       <c r="B2" t="n">
-        <v>80132</v>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hivikilen, Hivikilen, Hls</t>
+          <t>Marstrandmyran, Marstrandmyran, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>499290</v>
+        <v>499461</v>
       </c>
       <c r="R2" t="n">
-        <v>6846237</v>
+        <v>6845884</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127448660</v>
+        <v>127448386</v>
       </c>
       <c r="B3" t="n">
-        <v>80133</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Marstrandmyran, Marstrandmyran, Hls</t>
+          <t>Hivikilen, Hivikilen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>499461</v>
+        <v>499513</v>
       </c>
       <c r="R3" t="n">
-        <v>6845884</v>
+        <v>6845882</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -843,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Lunglav 4 meter från bandning i anmälan.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,12 +862,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -872,7 +877,7 @@
         <v>127448470</v>
       </c>
       <c r="B4" t="n">
-        <v>80132</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127448841</v>
+        <v>127448817</v>
       </c>
       <c r="B5" t="n">
-        <v>80132</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>499529</v>
+        <v>499501</v>
       </c>
       <c r="R5" t="n">
-        <v>6845885</v>
+        <v>6845889</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,57 +1068,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127448201</v>
+        <v>127448841</v>
       </c>
       <c r="B6" t="n">
-        <v>98470</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hivikilen, Hivikilen, Hls</t>
+          <t>Marstrandmyran, Marstrandmyran, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>499458</v>
+        <v>499529</v>
       </c>
       <c r="R6" t="n">
         <v>6845885</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1143,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Bestånd av knärot 7 meter från avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1162,12 +1153,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1177,7 +1168,7 @@
         <v>127449070</v>
       </c>
       <c r="B7" t="n">
-        <v>80132</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127450133</v>
+        <v>127449822</v>
       </c>
       <c r="B8" t="n">
-        <v>80132</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,17 +1293,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hivikilen, Hivikilen, Hls</t>
+          <t>Marstrandmyran, Marstrandmyran, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>499514</v>
+        <v>499384</v>
       </c>
       <c r="R8" t="n">
-        <v>6846240</v>
+        <v>6846045</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,11 +1333,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>6 meter från bandning.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1361,12 +1347,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1376,7 +1362,7 @@
         <v>127450046</v>
       </c>
       <c r="B9" t="n">
-        <v>80132</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127449822</v>
+        <v>127450133</v>
       </c>
       <c r="B10" t="n">
-        <v>80132</v>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,17 +1487,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Marstrandmyran, Marstrandmyran, Hls</t>
+          <t>Hivikilen, Hivikilen, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>499384</v>
+        <v>499514</v>
       </c>
       <c r="R10" t="n">
-        <v>6846045</v>
+        <v>6846240</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1541,6 +1527,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>6 meter från bandning.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1555,22 +1546,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127448817</v>
+        <v>127450593</v>
       </c>
       <c r="B11" t="n">
-        <v>80132</v>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1598,17 +1589,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Marstrandmyran, Marstrandmyran, Hls</t>
+          <t>Hivikilen, Hivikilen, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>499501</v>
+        <v>499290</v>
       </c>
       <c r="R11" t="n">
-        <v>6845889</v>
+        <v>6846237</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1652,60 +1643,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127448386</v>
+        <v>127449838</v>
       </c>
       <c r="B12" t="n">
-        <v>80132</v>
+        <v>80468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hivikilen, Hivikilen, Hls</t>
+          <t>Marstrandmyran, Marstrandmyran, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>499513</v>
+        <v>499391</v>
       </c>
       <c r="R12" t="n">
-        <v>6845882</v>
+        <v>6846036</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1735,11 +1726,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Lunglav 4 meter från bandning i anmälan.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1754,12 +1740,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1769,7 +1755,7 @@
         <v>127449478</v>
       </c>
       <c r="B13" t="n">
-        <v>57832</v>
+        <v>58114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1860,6 +1846,214 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127450785</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Marstrandmyran, Marstrandmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>499189</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6846015</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127448201</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hivikilen, Hivikilen, Hls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>499458</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6845885</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Bestånd av knärot 7 meter från avverkningsanmälan.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37833-2025 artfynd.xlsx
+++ b/artfynd/A 37833-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127448660</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127448386</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127448470</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127448817</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127448841</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127449070</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127449822</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127450046</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127450133</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127450593</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1749,6 +1804,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127449838</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1846,6 +1906,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127449478</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1943,6 +2008,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127450785</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2054,8 +2124,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127448201</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>